--- a/Project Outputs for UZ_PER_SiC_inverter_828xcc/Rev01/BOM/BOM_JLC-UZ_PER_SiC_inverter_828xcc.xlsx
+++ b/Project Outputs for UZ_PER_SiC_inverter_828xcc/Rev01/BOM/BOM_JLC-UZ_PER_SiC_inverter_828xcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_per_sic_inverter_828xcc\Project Outputs for UZ_PER_SiC_inverter_828xcc\Rev01\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F361966-186C-4F4F-B994-447BBDA05E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5768D4D8-ABFF-4CC8-BE63-A7F25A6EF4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="74055" yWindow="15" windowWidth="19125" windowHeight="10035" xr2:uid="{E740077A-DE3A-4E71-8ADE-FB65A92BCC9A}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{2B279F93-689D-4597-BA69-2775D0F7490C}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC-UZ_PER_SiC_inverter_828" sheetId="1" r:id="rId1"/>
@@ -650,7 +650,7 @@
     <t>R1, R2</t>
   </si>
   <si>
-    <t xml:space="preserve">KOA Speer	</t>
+    <t>KOA Speer</t>
   </si>
   <si>
     <t>SMD resistor E24 series</t>
@@ -1302,7 +1302,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9225DD1A-2D23-4E40-B9C7-97A3E5E7729D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A37BEA-836C-4387-BF0A-90D36726FEC3}">
   <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
